--- a/Global Arriendos/informe Global ARRIENDOS.xlsx
+++ b/Global Arriendos/informe Global ARRIENDOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\Global Arriendos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\Global Arriendos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44469883-EB55-44EF-8AD8-D629FB416B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A9AD13-3A05-4833-AB6D-D76F7A467E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COLORES " sheetId="1" r:id="rId1"/>
@@ -7346,30 +7346,30 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -30044,17 +30044,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="710" t="s">
+      <c r="A1" s="727" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="711"/>
-      <c r="C1" s="711"/>
-      <c r="D1" s="711"/>
-      <c r="E1" s="711"/>
-      <c r="F1" s="711"/>
-      <c r="G1" s="711"/>
-      <c r="H1" s="711"/>
-      <c r="I1" s="711"/>
+      <c r="B1" s="726"/>
+      <c r="C1" s="726"/>
+      <c r="D1" s="726"/>
+      <c r="E1" s="726"/>
+      <c r="F1" s="726"/>
+      <c r="G1" s="726"/>
+      <c r="H1" s="726"/>
+      <c r="I1" s="726"/>
       <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
@@ -30070,49 +30070,49 @@
       <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="714" t="s">
+      <c r="A3" s="719" t="s">
         <v>285</v>
       </c>
-      <c r="B3" s="715"/>
-      <c r="C3" s="713"/>
-      <c r="D3" s="712" t="s">
+      <c r="B3" s="717"/>
+      <c r="C3" s="718"/>
+      <c r="D3" s="720" t="s">
         <v>286</v>
       </c>
-      <c r="E3" s="713"/>
+      <c r="E3" s="718"/>
       <c r="F3" s="57"/>
-      <c r="G3" s="714" t="s">
+      <c r="G3" s="719" t="s">
         <v>287</v>
       </c>
-      <c r="H3" s="715"/>
-      <c r="I3" s="713"/>
-      <c r="J3" s="712" t="s">
+      <c r="H3" s="717"/>
+      <c r="I3" s="718"/>
+      <c r="J3" s="720" t="s">
         <v>288</v>
       </c>
-      <c r="K3" s="713"/>
-      <c r="M3" s="716" t="s">
+      <c r="K3" s="718"/>
+      <c r="M3" s="710" t="s">
         <v>289</v>
       </c>
-      <c r="N3" s="717"/>
+      <c r="N3" s="711"/>
       <c r="O3" s="709"/>
-      <c r="P3" s="716" t="s">
+      <c r="P3" s="710" t="s">
         <v>290</v>
       </c>
       <c r="Q3" s="709"/>
-      <c r="S3" s="716" t="s">
+      <c r="S3" s="710" t="s">
         <v>291</v>
       </c>
-      <c r="T3" s="717"/>
+      <c r="T3" s="711"/>
       <c r="U3" s="709"/>
-      <c r="V3" s="716" t="s">
+      <c r="V3" s="710" t="s">
         <v>292</v>
       </c>
       <c r="W3" s="709"/>
-      <c r="Y3" s="716" t="s">
+      <c r="Y3" s="710" t="s">
         <v>293</v>
       </c>
-      <c r="Z3" s="717"/>
+      <c r="Z3" s="711"/>
       <c r="AA3" s="709"/>
-      <c r="AB3" s="716" t="s">
+      <c r="AB3" s="710" t="s">
         <v>294</v>
       </c>
       <c r="AC3" s="709"/>
@@ -30610,49 +30610,49 @@
       <c r="F12" s="57"/>
     </row>
     <row r="13" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="724" t="s">
+      <c r="A13" s="723" t="s">
         <v>301</v>
       </c>
       <c r="B13" s="709"/>
       <c r="C13" s="57"/>
-      <c r="D13" s="725" t="s">
+      <c r="D13" s="724" t="s">
         <v>302</v>
       </c>
-      <c r="E13" s="713"/>
+      <c r="E13" s="718"/>
       <c r="F13" s="57"/>
-      <c r="G13" s="724" t="s">
+      <c r="G13" s="723" t="s">
         <v>303</v>
       </c>
       <c r="H13" s="709"/>
       <c r="I13" s="57"/>
-      <c r="J13" s="708" t="s">
+      <c r="J13" s="712" t="s">
         <v>304</v>
       </c>
       <c r="K13" s="709"/>
-      <c r="M13" s="708" t="s">
+      <c r="M13" s="712" t="s">
         <v>305</v>
       </c>
       <c r="N13" s="709"/>
       <c r="O13" s="57"/>
-      <c r="P13" s="708" t="s">
+      <c r="P13" s="712" t="s">
         <v>306</v>
       </c>
       <c r="Q13" s="709"/>
-      <c r="S13" s="708" t="s">
+      <c r="S13" s="712" t="s">
         <v>307</v>
       </c>
       <c r="T13" s="709"/>
       <c r="U13" s="57"/>
-      <c r="V13" s="708" t="s">
+      <c r="V13" s="712" t="s">
         <v>308</v>
       </c>
       <c r="W13" s="709"/>
-      <c r="Y13" s="708" t="s">
+      <c r="Y13" s="712" t="s">
         <v>309</v>
       </c>
       <c r="Z13" s="709"/>
       <c r="AA13" s="57"/>
-      <c r="AB13" s="708" t="s">
+      <c r="AB13" s="712" t="s">
         <v>308</v>
       </c>
       <c r="AC13" s="709"/>
@@ -30729,63 +30729,63 @@
       <c r="F16" s="57"/>
     </row>
     <row r="17" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="718" t="s">
+      <c r="A17" s="713" t="s">
         <v>313</v>
       </c>
-      <c r="B17" s="719"/>
-      <c r="C17" s="719"/>
-      <c r="D17" s="720"/>
+      <c r="B17" s="714"/>
+      <c r="C17" s="714"/>
+      <c r="D17" s="715"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="718" t="s">
+      <c r="G17" s="713" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="719"/>
-      <c r="I17" s="719"/>
-      <c r="J17" s="720"/>
-      <c r="M17" s="718" t="s">
+      <c r="H17" s="714"/>
+      <c r="I17" s="714"/>
+      <c r="J17" s="715"/>
+      <c r="M17" s="713" t="s">
         <v>314</v>
       </c>
-      <c r="N17" s="719"/>
-      <c r="O17" s="719"/>
-      <c r="P17" s="720"/>
-      <c r="S17" s="718" t="s">
+      <c r="N17" s="714"/>
+      <c r="O17" s="714"/>
+      <c r="P17" s="715"/>
+      <c r="S17" s="713" t="s">
         <v>4</v>
       </c>
-      <c r="T17" s="719"/>
-      <c r="U17" s="719"/>
-      <c r="V17" s="720"/>
-      <c r="Y17" s="718" t="s">
+      <c r="T17" s="714"/>
+      <c r="U17" s="714"/>
+      <c r="V17" s="715"/>
+      <c r="Y17" s="713" t="s">
         <v>5</v>
       </c>
-      <c r="Z17" s="719"/>
-      <c r="AA17" s="719"/>
-      <c r="AB17" s="720"/>
+      <c r="Z17" s="714"/>
+      <c r="AA17" s="714"/>
+      <c r="AB17" s="715"/>
     </row>
     <row r="18" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="721"/>
-      <c r="B18" s="715"/>
-      <c r="C18" s="715"/>
-      <c r="D18" s="713"/>
+      <c r="A18" s="716"/>
+      <c r="B18" s="717"/>
+      <c r="C18" s="717"/>
+      <c r="D18" s="718"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="721"/>
-      <c r="H18" s="715"/>
-      <c r="I18" s="715"/>
-      <c r="J18" s="713"/>
-      <c r="M18" s="721"/>
-      <c r="N18" s="715"/>
-      <c r="O18" s="715"/>
-      <c r="P18" s="713"/>
-      <c r="S18" s="721"/>
-      <c r="T18" s="715"/>
-      <c r="U18" s="715"/>
-      <c r="V18" s="713"/>
-      <c r="Y18" s="721"/>
-      <c r="Z18" s="715"/>
-      <c r="AA18" s="715"/>
-      <c r="AB18" s="713"/>
+      <c r="G18" s="716"/>
+      <c r="H18" s="717"/>
+      <c r="I18" s="717"/>
+      <c r="J18" s="718"/>
+      <c r="M18" s="716"/>
+      <c r="N18" s="717"/>
+      <c r="O18" s="717"/>
+      <c r="P18" s="718"/>
+      <c r="S18" s="716"/>
+      <c r="T18" s="717"/>
+      <c r="U18" s="717"/>
+      <c r="V18" s="718"/>
+      <c r="Y18" s="716"/>
+      <c r="Z18" s="717"/>
+      <c r="AA18" s="717"/>
+      <c r="AB18" s="718"/>
     </row>
     <row r="19" spans="1:28" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="726" t="s">
+      <c r="A19" s="708" t="s">
         <v>315</v>
       </c>
       <c r="B19" s="709"/>
@@ -30796,7 +30796,7 @@
         <v>317</v>
       </c>
       <c r="F19" s="57"/>
-      <c r="G19" s="726" t="s">
+      <c r="G19" s="708" t="s">
         <v>315</v>
       </c>
       <c r="H19" s="709"/>
@@ -30806,7 +30806,7 @@
       <c r="J19" s="98" t="s">
         <v>317</v>
       </c>
-      <c r="M19" s="726" t="s">
+      <c r="M19" s="708" t="s">
         <v>315</v>
       </c>
       <c r="N19" s="709"/>
@@ -30816,7 +30816,7 @@
       <c r="P19" s="98" t="s">
         <v>317</v>
       </c>
-      <c r="S19" s="726" t="s">
+      <c r="S19" s="708" t="s">
         <v>315</v>
       </c>
       <c r="T19" s="709"/>
@@ -30826,7 +30826,7 @@
       <c r="V19" s="98" t="s">
         <v>317</v>
       </c>
-      <c r="Y19" s="726" t="s">
+      <c r="Y19" s="708" t="s">
         <v>315</v>
       </c>
       <c r="Z19" s="709"/>
@@ -31188,12 +31188,12 @@
     <row r="29" spans="1:28" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:28" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:28" ht="22.8" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="727" t="s">
+      <c r="A31" s="725" t="s">
         <v>323</v>
       </c>
-      <c r="B31" s="711"/>
-      <c r="C31" s="711"/>
-      <c r="D31" s="711"/>
+      <c r="B31" s="726"/>
+      <c r="C31" s="726"/>
+      <c r="D31" s="726"/>
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
@@ -31578,10 +31578,10 @@
       <c r="N49" s="15"/>
     </row>
     <row r="52" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="722" t="s">
+      <c r="A52" s="721" t="s">
         <v>349</v>
       </c>
-      <c r="B52" s="723"/>
+      <c r="B52" s="722"/>
     </row>
     <row r="53" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="108" t="s">
@@ -31787,18 +31787,11 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="Y19:Z19"/>
-    <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="AB13:AC13"/>
-    <mergeCell ref="Y17:AB18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="S17:V18"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="M3:O3"/>
     <mergeCell ref="M17:P18"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:K3"/>
@@ -31815,11 +31808,18 @@
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="S17:V18"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="Y3:AA3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="Y13:Z13"/>
+    <mergeCell ref="AB13:AC13"/>
+    <mergeCell ref="Y17:AB18"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -31862,14 +31862,14 @@
       <c r="A2" s="728" t="s">
         <v>354</v>
       </c>
-      <c r="B2" s="715"/>
-      <c r="C2" s="715"/>
-      <c r="D2" s="715"/>
-      <c r="E2" s="715"/>
-      <c r="F2" s="715"/>
-      <c r="G2" s="715"/>
-      <c r="H2" s="715"/>
-      <c r="I2" s="715"/>
+      <c r="B2" s="717"/>
+      <c r="C2" s="717"/>
+      <c r="D2" s="717"/>
+      <c r="E2" s="717"/>
+      <c r="F2" s="717"/>
+      <c r="G2" s="717"/>
+      <c r="H2" s="717"/>
+      <c r="I2" s="717"/>
       <c r="J2" s="505"/>
       <c r="K2" s="505"/>
       <c r="L2" s="505"/>
@@ -32656,15 +32656,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096B3B8095E610F46997987F627BA2050" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b3bbc42fd73bed8b4972cfac315545d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e7be84e2-caba-498a-9078-d8746d97147d" xmlns:ns3="364b9ec1-f1ed-4c2d-8f06-e465d44f7fe6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9231a099640da205526a21db75d4eba4" ns2:_="" ns3:_="">
     <xsd:import namespace="e7be84e2-caba-498a-9078-d8746d97147d"/>
@@ -32869,6 +32860,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -32881,14 +32881,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D143046-DCAF-400F-AAF8-4BBC718C1BD9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D29372E9-4A50-440A-97BA-AD99D95CD3C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32907,6 +32899,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D143046-DCAF-400F-AAF8-4BBC718C1BD9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC22CD36-AFB1-4957-9C99-E2B7FFF10FAB}">
   <ds:schemaRefs>
